--- a/data/trans_dic/IP2907_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial</t>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,65; 25,13</t>
+          <t>13,56; 26,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,21; 38,29</t>
+          <t>19,06; 40,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,86; 30,82</t>
+          <t>18,71; 30,96</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,88; 22,34</t>
+          <t>13,11; 22,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 22,0</t>
+          <t>13,11; 22,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,38; 20,65</t>
+          <t>14,16; 20,79</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,43; 25,26</t>
+          <t>14,52; 25,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,6; 26,45</t>
+          <t>13,48; 26,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 23,52</t>
+          <t>15,44; 23,69</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 26,3</t>
+          <t>15,68; 26,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,03; 23,65</t>
+          <t>13,09; 23,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,59; 23,3</t>
+          <t>15,87; 23,14</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,75; 22,03</t>
+          <t>16,35; 21,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,02; 23,25</t>
+          <t>16,96; 23,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,55; 21,82</t>
+          <t>17,51; 21,83</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>21450</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38071</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59521</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>15328; 29485</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25879; 54726</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>46565; 77040</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>31785</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42223</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74008</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>24160; 40626</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32158; 54797</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>60818; 89305</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>30950</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34357</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65307</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>23128; 41045</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24423; 47405</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52572; 80650</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>33241</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31256</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>64497</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>25153; 42408</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22929; 40300</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>53255; 77630</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>117425</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>145907</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>263332</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>100877; 132963</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>125043; 172695</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>237069; 295702</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2907_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 26,08</t>
+          <t>13,5; 25,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 40,31</t>
+          <t>18,67; 39,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,71; 30,96</t>
+          <t>18,39; 30,84</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,11; 22,05</t>
+          <t>13,18; 21,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,11; 22,34</t>
+          <t>13,17; 22,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,16; 20,79</t>
+          <t>14,03; 20,61</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,52; 25,77</t>
+          <t>14,07; 25,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,48; 26,17</t>
+          <t>13,64; 27,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,44; 23,69</t>
+          <t>15,32; 23,68</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,68; 26,44</t>
+          <t>15,65; 25,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,09; 23,01</t>
+          <t>13,06; 23,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,87; 23,14</t>
+          <t>15,78; 23,16</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,55</t>
+          <t>16,22; 21,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,96; 23,42</t>
+          <t>17,17; 23,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,51; 21,83</t>
+          <t>17,44; 21,46</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15328; 29485</t>
+          <t>15266; 28937</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25879; 54726</t>
+          <t>25339; 53343</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46565; 77040</t>
+          <t>45754; 76741</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24160; 40626</t>
+          <t>24285; 39827</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32158; 54797</t>
+          <t>32287; 54029</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60818; 89305</t>
+          <t>60275; 88546</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23128; 41045</t>
+          <t>22418; 40164</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24423; 47405</t>
+          <t>24715; 50271</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52572; 80650</t>
+          <t>52163; 80602</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25153; 42408</t>
+          <t>25104; 41547</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22929; 40300</t>
+          <t>22877; 41414</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53255; 77630</t>
+          <t>52941; 77713</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>100877; 132963</t>
+          <t>100103; 135554</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>125043; 172695</t>
+          <t>126570; 171111</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>237069; 295702</t>
+          <t>236214; 290681</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2907_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 25,59</t>
+          <t>16,89; 32,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 39,29</t>
+          <t>13,38; 24,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,39; 30,84</t>
+          <t>17,16; 27,17</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 21,61</t>
+          <t>12,85; 21,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 22,03</t>
+          <t>12,63; 21,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 20,61</t>
+          <t>14,03; 20,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 25,22</t>
+          <t>14,24; 28,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,64; 27,75</t>
+          <t>15,56; 26,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,32; 23,68</t>
+          <t>16,32; 24,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,65; 25,9</t>
+          <t>12,98; 23,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 23,65</t>
+          <t>15,63; 26,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,78; 23,16</t>
+          <t>15,61; 23,33</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 21,97</t>
+          <t>16,43; 22,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 23,21</t>
+          <t>16,83; 22,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,44; 21,46</t>
+          <t>17,38; 21,55</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21450</t>
+          <t>30185</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38071</t>
+          <t>21854</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59521</t>
+          <t>52039</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15266; 28937</t>
+          <t>20592; 39750</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25339; 53343</t>
+          <t>15623; 28870</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45754; 76741</t>
+          <t>40956; 64845</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74008</t>
+          <t>68693</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24285; 39827</t>
+          <t>29407; 49462</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32287; 54029</t>
+          <t>22550; 38693</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60275; 88546</t>
+          <t>57183; 83278</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>32598</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34357</t>
+          <t>31108</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65307</t>
+          <t>63706</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22418; 40164</t>
+          <t>23444; 46492</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24715; 50271</t>
+          <t>23366; 40348</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52163; 80602</t>
+          <t>51363; 77905</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>29373</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64497</t>
+          <t>62516</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25104; 41547</t>
+          <t>21303; 38429</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22877; 41414</t>
+          <t>24949; 42006</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52941; 77713</t>
+          <t>50537; 75541</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>178</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>117425</t>
+          <t>130749</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>145907</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>263332</t>
+          <t>246954</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>100103; 135554</t>
+          <t>111678; 150256</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>126570; 171111</t>
+          <t>101842; 133829</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>236214; 290681</t>
+          <t>223274; 276884</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2907_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>16,89; 32,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13,38; 24,73</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17,16; 27,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>12,85; 21,61</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12,63; 21,67</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14,03; 20,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19,8%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>14,24; 28,24</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15,56; 26,88</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>16,32; 24,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>12,98; 23,42</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15,63; 26,31</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15,61; 23,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>16,43; 22,11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16,83; 22,12</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17,38; 21,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2476289130723913</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1871929068245668</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.218063094850127</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>30185</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21854</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52039</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1689309267555892</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1338250298116852</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1716210791913643</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>20592; 39750</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15623; 28870</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>40956; 64845</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3260992917725907</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.2472895305222365</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2717277353339322</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.168589133694553</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1685531239080754</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1685733529400977</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>38593</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>30100</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68693</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1284616917169777</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1262741808217633</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1403277992085476</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>29407; 49462</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>22550; 38693</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>57183; 83278</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2160656773824967</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2166686950680706</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2043638132854107</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1979735671355254</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.2072222683034972</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2023843627951391</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>32598</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>31108</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63706</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1423823205091534</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1556498435814118</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1631713810952901</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>23444; 46492</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>23366; 40348</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51363; 77905</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2823547653908657</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2687730798685454</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2474938018417761</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1789853985715643</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2075867610231103</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1930892886459447</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>29373</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>33142</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>62516</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1298113570742734</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1562675705870935</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1560926458838209</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>21303; 38429</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>24949; 42006</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>50537; 75541</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2341652115056952</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2631022912800298</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2333214936078205</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1923965303494996</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1920418396847021</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1922294667789481</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>130749</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>116205</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>246954</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1643337802569707</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1683063272908316</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1737970923602891</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>111678; 150256</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>101842; 133829</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>223274; 276884</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.221101438407431</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.2211683531009249</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.2155273301388264</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>30185</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>21854</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>52039</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>20592</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>15623</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>40956</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>39750</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>28870</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>64845</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>38593</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>30100</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>68693</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>29407</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>22550</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>57183</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>49462</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>38693</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>83278</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>32598</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>31108</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>63706</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>23444</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>23366</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>51363</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>46492</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>40348</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>77905</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>29373</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>33142</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>62516</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>21303</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>24949</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>50537</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>38429</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>42006</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>75541</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>130749</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>116205</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>246954</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>111678</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>101842</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>223274</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>150256</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>133829</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>276884</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>